--- a/imports/Herramienta.xlsx
+++ b/imports/Herramienta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Limpieza\LIMPIEZA_APP\sop_lavado_app\imports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBBEE59E-8DF8-485F-B042-295DC6921801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E390F771-4D59-4712-8DCB-570532A2C784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Kit" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Herramienta!$A$2:$G$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Herramienta!$A$2:$G$42</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="252">
   <si>
     <t>HE</t>
   </si>
@@ -361,9 +361,6 @@
     <t>HE-TP-001</t>
   </si>
   <si>
-    <t>Mop de polvo</t>
-  </si>
-  <si>
     <t>HE-MO-002</t>
   </si>
   <si>
@@ -580,9 +577,6 @@
     <t>Kit Vidrios Superior</t>
   </si>
   <si>
-    <t>Kit Vidrios Inferior</t>
-  </si>
-  <si>
     <t>KT-BA-001</t>
   </si>
   <si>
@@ -652,9 +646,6 @@
     <t>Tallar Baño - WC Interior</t>
   </si>
   <si>
-    <t>Limpiar Vidrios Superior</t>
-  </si>
-  <si>
     <t>Limpiar Vidrios Inferior</t>
   </si>
   <si>
@@ -748,9 +739,6 @@
     <t>FR-SA-001</t>
   </si>
   <si>
-    <t>KT-VI-003</t>
-  </si>
-  <si>
     <t>003</t>
   </si>
   <si>
@@ -758,6 +746,57 @@
   </si>
   <si>
     <t>Limpiar Vidrios</t>
+  </si>
+  <si>
+    <t>Kit Electronicos</t>
+  </si>
+  <si>
+    <t>KT-SA-002</t>
+  </si>
+  <si>
+    <t>Sacudir Electronicos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kit Electronicos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sacudir Electronicos </t>
+  </si>
+  <si>
+    <t>KT-SA-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sacudir No Reusables </t>
+  </si>
+  <si>
+    <t>Mop Polvo</t>
+  </si>
+  <si>
+    <t>Kit Paño Vidrios</t>
+  </si>
+  <si>
+    <t>Kit Multiusos</t>
+  </si>
+  <si>
+    <t>Sacudir Multiusos</t>
+  </si>
+  <si>
+    <t>ACOMODAR</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>KT-TA-001</t>
+  </si>
+  <si>
+    <t>Kit Lavar Trastes</t>
+  </si>
+  <si>
+    <t>Lavar Trastes</t>
+  </si>
+  <si>
+    <t>FR-TA-001</t>
   </si>
 </sst>
 </file>
@@ -954,7 +993,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1055,11 +1094,62 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="56">
+  <dxfs count="65">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1670,7 +1760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.73046875" customWidth="1"/>
@@ -1749,7 +1839,7 @@
         <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>69</v>
@@ -1774,7 +1864,7 @@
         <v>58</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -1785,7 +1875,7 @@
         <v>64</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>69</v>
@@ -1810,7 +1900,7 @@
         <v>59</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -1821,7 +1911,7 @@
         <v>48</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>69</v>
@@ -1851,7 +1941,7 @@
         <v>54</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>69</v>
@@ -1881,7 +1971,7 @@
         <v>70</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>69</v>
@@ -1909,10 +1999,10 @@
         <v>96</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>69</v>
@@ -1943,7 +2033,7 @@
         <v>47</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>69</v>
@@ -1974,7 +2064,7 @@
         <v>72</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>69</v>
@@ -2005,7 +2095,7 @@
         <v>47</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>69</v>
@@ -2034,7 +2124,7 @@
         <v>77</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>69</v>
@@ -2063,7 +2153,7 @@
         <v>91</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>69</v>
@@ -2092,7 +2182,7 @@
         <v>76</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>69</v>
@@ -2121,7 +2211,7 @@
         <v>53</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>69</v>
@@ -2150,7 +2240,7 @@
         <v>47</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>69</v>
@@ -2179,7 +2269,7 @@
         <v>47</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>69</v>
@@ -2208,7 +2298,7 @@
         <v>47</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>69</v>
@@ -2223,7 +2313,7 @@
         <v>5</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>24</v>
@@ -2237,7 +2327,7 @@
         <v>79</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>69</v>
@@ -2266,7 +2356,7 @@
         <v>79</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>69</v>
@@ -2292,10 +2382,10 @@
         <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>69</v>
@@ -2324,7 +2414,7 @@
         <v>76</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>69</v>
@@ -2353,7 +2443,7 @@
         <v>49</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>69</v>
@@ -2382,7 +2472,7 @@
         <v>49</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>69</v>
@@ -2411,7 +2501,7 @@
         <v>57</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>69</v>
@@ -2440,7 +2530,7 @@
         <v>83</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>69</v>
@@ -2484,10 +2574,10 @@
         <v>1</v>
       </c>
       <c r="I27" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J27" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="8" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -2498,7 +2588,7 @@
         <v>51</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>69</v>
@@ -2527,7 +2617,7 @@
         <v>45</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>69</v>
@@ -2546,13 +2636,13 @@
     </row>
     <row r="30" spans="1:10" s="8" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>69</v>
@@ -2571,13 +2661,13 @@
     </row>
     <row r="31" spans="1:10" s="8" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>69</v>
@@ -2596,13 +2686,13 @@
     </row>
     <row r="32" spans="1:10" s="8" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>106</v>
+        <v>242</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>69</v>
@@ -2621,13 +2711,13 @@
     </row>
     <row r="33" spans="1:13" s="8" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>69</v>
@@ -2636,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G33" s="10">
         <v>1</v>
@@ -2649,10 +2739,10 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>69</v>
@@ -2674,10 +2764,10 @@
         <v>65</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>69</v>
@@ -2702,7 +2792,7 @@
         <v>45</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>69</v>
@@ -2721,13 +2811,13 @@
     </row>
     <row r="37" spans="1:13" s="8" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>69</v>
@@ -2746,13 +2836,13 @@
     </row>
     <row r="38" spans="1:13" s="8" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>69</v>
@@ -2773,13 +2863,13 @@
     </row>
     <row r="39" spans="1:13" s="8" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>69</v>
@@ -2806,7 +2896,7 @@
         <v>81</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>69</v>
@@ -2823,13 +2913,13 @@
     </row>
     <row r="41" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>69</v>
@@ -2846,13 +2936,13 @@
     </row>
     <row r="42" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>69</v>
@@ -2867,9 +2957,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="20"/>
     </row>
+    <row r="44" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <autoFilter ref="A2:G42" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="4">
@@ -2879,53 +2970,53 @@
     <mergeCell ref="L1:M1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:A42">
-    <cfRule type="duplicateValues" dxfId="55" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4">
-    <cfRule type="duplicateValues" dxfId="54" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A34">
-    <cfRule type="duplicateValues" dxfId="53" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A35">
-    <cfRule type="duplicateValues" dxfId="52" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A36 A1:A3 A5:A33 A38:A1048576">
-    <cfRule type="duplicateValues" dxfId="51" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37">
-    <cfRule type="duplicateValues" dxfId="50" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13">
-    <cfRule type="duplicateValues" dxfId="49" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14">
-    <cfRule type="duplicateValues" dxfId="47" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="6"/>
     <cfRule type="duplicateValues" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="44" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="2"/>
     <cfRule type="duplicateValues" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:J22">
-    <cfRule type="duplicateValues" dxfId="41" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:J22">
     <cfRule type="duplicateValues" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:J28">
-    <cfRule type="duplicateValues" dxfId="40" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:J43">
-    <cfRule type="duplicateValues" dxfId="39" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I23:J24">
-    <cfRule type="duplicateValues" dxfId="38" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="19"/>
     <cfRule type="duplicateValues" priority="20"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2935,14 +3026,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:K1048576"/>
+  <dimension ref="A1:K1048575"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.46484375" customWidth="1"/>
     <col min="2" max="2" width="13.19921875" customWidth="1"/>
     <col min="3" max="3" width="26.796875" customWidth="1"/>
     <col min="4" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" customWidth="1"/>
+    <col min="7" max="7" width="18.3984375" customWidth="1"/>
     <col min="8" max="8" width="15.59765625" customWidth="1"/>
     <col min="9" max="9" width="7.06640625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
@@ -2964,10 +3055,10 @@
         <v>20</v>
       </c>
       <c r="H1" s="35"/>
-      <c r="J1" s="29" t="s">
+      <c r="J1" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="30"/>
+      <c r="K1" s="27"/>
     </row>
     <row r="2" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="16" t="s">
@@ -2983,13 +3074,13 @@
         <v>13</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F2" s="17" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="18" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H2" s="18" t="s">
         <v>15</v>
@@ -3003,13 +3094,13 @@
     </row>
     <row r="3" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>93</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>23</v>
@@ -3021,45 +3112,45 @@
         <v>1</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>23</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F4" s="15">
         <v>1</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>24</v>
@@ -3067,31 +3158,31 @@
     </row>
     <row r="5" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>23</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F5" s="15">
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>56</v>
@@ -3099,63 +3190,63 @@
     </row>
     <row r="6" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>23</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F6" s="15">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>178</v>
+        <v>233</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>23</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F7" s="15">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>39</v>
@@ -3163,42 +3254,42 @@
     </row>
     <row r="8" spans="1:11" s="12" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>178</v>
+        <v>233</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>23</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F8" s="15">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="11" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>218</v>
+        <v>178</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>179</v>
@@ -3206,20 +3297,20 @@
       <c r="D9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="F9" s="21">
-        <v>2</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>204</v>
+      <c r="E9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="15">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>92</v>
@@ -3227,13 +3318,13 @@
     </row>
     <row r="10" spans="1:11" s="11" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>23</v>
@@ -3245,348 +3336,354 @@
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="11" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="22" t="s">
         <v>180</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D11" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="F11" s="15">
         <v>1</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="2" t="s">
         <v>200</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J11" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="11" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="22" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F12" s="15">
-        <v>1</v>
+        <v>122</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>226</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>202</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="11" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="22" t="s">
-        <v>222</v>
+        <v>182</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F13" s="23" t="s">
-        <v>229</v>
+        <v>122</v>
+      </c>
+      <c r="F13" s="21">
+        <v>3</v>
       </c>
       <c r="G13" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="11" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="22" t="s">
         <v>205</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" s="11" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="22" t="s">
-        <v>184</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>185</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F14" s="21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F15" s="21">
         <v>4</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F16" s="21">
         <v>4</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F17" s="21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F18" s="21">
         <v>5</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F19" s="21">
         <v>5</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="22" t="s">
-        <v>225</v>
+        <v>60</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>186</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F20" s="21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F21" s="21">
         <v>6</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F22" s="21">
         <v>6</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="1" t="s">
-        <v>226</v>
+      <c r="A23" s="22" t="s">
+        <v>187</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>188</v>
@@ -3595,27 +3692,27 @@
         <v>23</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F23" s="21">
-        <v>6</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>198</v>
+        <v>56</v>
+      </c>
+      <c r="F23" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="22" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>23</v>
@@ -3624,24 +3721,24 @@
         <v>56</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="22" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>23</v>
@@ -3650,24 +3747,24 @@
         <v>56</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="22" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>23</v>
@@ -3676,24 +3773,24 @@
         <v>56</v>
       </c>
       <c r="F26" s="23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="22" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>23</v>
@@ -3702,104 +3799,177 @@
         <v>56</v>
       </c>
       <c r="F27" s="23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="22" t="s">
-        <v>189</v>
+        <v>228</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>190</v>
+        <v>229</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>230</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="22" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>191</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>233</v>
+        <v>226</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>201</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>204</v>
+        <v>226</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>237</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="32" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="33" spans="6:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F33" s="13"/>
-    </row>
-    <row r="34" spans="6:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="35" spans="6:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="36" spans="6:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="1048576" spans="7:8" x14ac:dyDescent="0.45">
-      <c r="G1048576" s="1"/>
-      <c r="H1048576" s="20"/>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="22" t="s">
+        <v>240</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F31" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="36" t="s">
+        <v>248</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F32" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="36" t="s">
+        <v>248</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F33" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="35" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="36" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="1048575" spans="7:8" x14ac:dyDescent="0.45">
+      <c r="G1048575" s="1"/>
+      <c r="H1048575" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3808,78 +3978,92 @@
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="G1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="37" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="44"/>
+  <conditionalFormatting sqref="B11">
+    <cfRule type="duplicateValues" dxfId="46" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="53"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="duplicateValues" dxfId="44" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15">
-    <cfRule type="duplicateValues" dxfId="35" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="33" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="31" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18">
-    <cfRule type="duplicateValues" dxfId="29" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19">
-    <cfRule type="duplicateValues" dxfId="27" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20">
-    <cfRule type="duplicateValues" dxfId="25" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="23" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="21" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="duplicateValues" dxfId="19" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24">
-    <cfRule type="duplicateValues" dxfId="17" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="13" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="11" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="duplicateValues" dxfId="14" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31">
+    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32:B33">
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32:B33">
+    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3:K8 K10">
-    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="3" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3887,7 +4071,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="12.06640625" customWidth="1"/>
@@ -3923,16 +4107,16 @@
         <v>27</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F2" s="18" t="s">
         <v>15</v>
@@ -3946,49 +4130,49 @@
     </row>
     <row r="3" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>24</v>
@@ -3996,25 +4180,25 @@
     </row>
     <row r="5" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C5" s="1">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>56</v>
@@ -4022,99 +4206,97 @@
     </row>
     <row r="6" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C6" s="1">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>218</v>
+        <v>178</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C7" s="1">
-        <v>3</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>204</v>
+      <c r="E7" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="22" t="s">
         <v>180</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="C8" s="1"/>
+        <v>218</v>
+      </c>
+      <c r="C8" s="19"/>
       <c r="D8" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>200</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="22" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="1" t="s">
-        <v>183</v>
+        <v>218</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="22" t="s">
+        <v>225</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>202</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>92</v>
@@ -4122,188 +4304,227 @@
     </row>
     <row r="10" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="22" t="s">
-        <v>222</v>
+        <v>182</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="C10" s="1"/>
+        <v>218</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1</v>
+      </c>
       <c r="D10" s="22" t="s">
-        <v>228</v>
+        <v>183</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="22" t="s">
-        <v>184</v>
+        <v>220</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C11" s="1">
-        <v>1</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="22" t="s">
-        <v>223</v>
-      </c>
       <c r="B12" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C12" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C13" s="1">
         <v>3</v>
       </c>
-      <c r="D13" s="22" t="s">
-        <v>225</v>
+      <c r="D13" s="1" t="s">
+        <v>186</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>198</v>
+        <v>203</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="1" t="s">
-        <v>226</v>
+      <c r="A14" s="22" t="s">
+        <v>187</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="C14" s="1">
-        <v>3</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="C14" s="19"/>
       <c r="D14" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>198</v>
+      <c r="E14" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>194</v>
       </c>
       <c r="J14" s="13"/>
     </row>
     <row r="15" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="22" t="s">
-        <v>189</v>
+        <v>228</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C15" s="19"/>
-      <c r="D15" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="D15" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>230</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="22" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="22" t="s">
-        <v>232</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>233</v>
-      </c>
       <c r="F16" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="22" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C17" s="19"/>
       <c r="D17" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E17" s="1" t="s">
         <v>238</v>
       </c>
+      <c r="E17" s="2" t="s">
+        <v>239</v>
+      </c>
       <c r="F17" s="9" t="s">
-        <v>196</v>
-      </c>
-    </row>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="22" t="s">
+        <v>240</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C18" s="19"/>
+      <c r="D18" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="36" t="s">
+        <v>248</v>
+      </c>
+      <c r="B19" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="C19" s="19"/>
+      <c r="D19" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="21" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="22" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="H1:I1"/>
   </mergeCells>
   <conditionalFormatting sqref="I3:I8 I10">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I11">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/imports/Herramienta.xlsx
+++ b/imports/Herramienta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Limpieza\LIMPIEZA_APP\sop_lavado_app\imports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E390F771-4D59-4712-8DCB-570532A2C784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE329C2F-96C9-47D4-81A3-4407C3D536F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="266">
   <si>
     <t>HE</t>
   </si>
@@ -532,9 +532,6 @@
     <t xml:space="preserve">Mop Vidrios </t>
   </si>
   <si>
-    <t>Mop Secado</t>
-  </si>
-  <si>
     <t>Base Mop</t>
   </si>
   <si>
@@ -797,6 +794,51 @@
   </si>
   <si>
     <t>FR-TA-001</t>
+  </si>
+  <si>
+    <t>HE-CE-004</t>
+  </si>
+  <si>
+    <t>Cepillo Plancha</t>
+  </si>
+  <si>
+    <t>KT-MS-001</t>
+  </si>
+  <si>
+    <t>Kit Mop Seco</t>
+  </si>
+  <si>
+    <t>Mopear</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>KT-SA-004</t>
+  </si>
+  <si>
+    <t>Kit Banquillo</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>Banquillo</t>
+  </si>
+  <si>
+    <t>Sacudir Banquillo</t>
+  </si>
+  <si>
+    <t>Kit Mop Humedo</t>
+  </si>
+  <si>
+    <t>KT-MH-001</t>
+  </si>
+  <si>
+    <t>Mop Humedo</t>
+  </si>
+  <si>
+    <t>FR-MH-001</t>
   </si>
 </sst>
 </file>
@@ -806,7 +848,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -839,6 +881,12 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -993,7 +1041,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1073,12 +1121,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1094,8 +1136,11 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1104,7 +1149,87 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="65">
+  <dxfs count="81">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -2153,7 +2278,7 @@
         <v>91</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>69</v>
@@ -2667,7 +2792,7 @@
         <v>70</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>163</v>
+        <v>264</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>69</v>
@@ -2692,7 +2817,7 @@
         <v>70</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>69</v>
@@ -2717,7 +2842,7 @@
         <v>109</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>69</v>
@@ -2742,7 +2867,7 @@
         <v>118</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>69</v>
@@ -2767,7 +2892,7 @@
         <v>118</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>69</v>
@@ -2792,7 +2917,7 @@
         <v>45</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>69</v>
@@ -2817,7 +2942,7 @@
         <v>45</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>69</v>
@@ -2842,7 +2967,7 @@
         <v>117</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>69</v>
@@ -2869,7 +2994,7 @@
         <v>85</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>69</v>
@@ -2896,7 +3021,7 @@
         <v>81</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>69</v>
@@ -2919,7 +3044,7 @@
         <v>81</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>69</v>
@@ -2942,7 +3067,7 @@
         <v>81</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>69</v>
@@ -2958,7 +3083,27 @@
       </c>
     </row>
     <row r="43" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="20"/>
+      <c r="A43" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G43" s="10">
+        <v>4</v>
+      </c>
     </row>
     <row r="44" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
@@ -2970,54 +3115,57 @@
     <mergeCell ref="L1:M1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:A42">
+    <cfRule type="duplicateValues" dxfId="80" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:A50">
+    <cfRule type="duplicateValues" dxfId="79" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4">
+    <cfRule type="duplicateValues" dxfId="78" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A34">
+    <cfRule type="duplicateValues" dxfId="77" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35">
+    <cfRule type="duplicateValues" dxfId="76" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A36 A1:A3 A5:A33 A38:A1048576">
+    <cfRule type="duplicateValues" dxfId="75" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A37">
+    <cfRule type="duplicateValues" dxfId="74" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="73" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="duplicateValues" dxfId="71" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="7"/>
+    <cfRule type="duplicateValues" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="68" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="3"/>
+    <cfRule type="duplicateValues" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:J22">
+    <cfRule type="duplicateValues" dxfId="65" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:J22">
+    <cfRule type="duplicateValues" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:J28">
     <cfRule type="duplicateValues" dxfId="64" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4">
-    <cfRule type="duplicateValues" dxfId="63" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A34">
-    <cfRule type="duplicateValues" dxfId="62" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A35">
-    <cfRule type="duplicateValues" dxfId="61" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A36 A1:A3 A5:A33 A38:A1048576">
-    <cfRule type="duplicateValues" dxfId="60" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A37">
-    <cfRule type="duplicateValues" dxfId="59" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="duplicateValues" dxfId="58" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="duplicateValues" dxfId="56" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="6"/>
-    <cfRule type="duplicateValues" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="53" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="2"/>
-    <cfRule type="duplicateValues" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I1:J22">
-    <cfRule type="duplicateValues" dxfId="50" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:J22">
-    <cfRule type="duplicateValues" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:J28">
-    <cfRule type="duplicateValues" dxfId="49" priority="11"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="I3:J43">
-    <cfRule type="duplicateValues" dxfId="48" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I23:J24">
-    <cfRule type="duplicateValues" dxfId="47" priority="19"/>
-    <cfRule type="duplicateValues" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="20"/>
+    <cfRule type="duplicateValues" priority="21"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3046,15 +3194,15 @@
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="32"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="34" t="s">
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="35"/>
+      <c r="H1" s="33"/>
       <c r="J1" s="27" t="s">
         <v>19</v>
       </c>
@@ -3080,7 +3228,7 @@
         <v>11</v>
       </c>
       <c r="G2" s="18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H2" s="18" t="s">
         <v>15</v>
@@ -3094,7 +3242,7 @@
     </row>
     <row r="3" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>93</v>
@@ -3112,10 +3260,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="H3" s="9" t="s">
         <v>193</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>194</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>125</v>
@@ -3126,13 +3274,13 @@
     </row>
     <row r="4" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>23</v>
@@ -3144,10 +3292,10 @@
         <v>1</v>
       </c>
       <c r="G4" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H4" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>126</v>
@@ -3158,7 +3306,7 @@
     </row>
     <row r="5" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>113</v>
@@ -3176,10 +3324,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>127</v>
@@ -3190,7 +3338,7 @@
     </row>
     <row r="6" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>33</v>
@@ -3208,10 +3356,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>128</v>
@@ -3222,13 +3370,13 @@
     </row>
     <row r="7" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>23</v>
@@ -3240,10 +3388,10 @@
         <v>1</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>129</v>
@@ -3254,13 +3402,13 @@
     </row>
     <row r="8" spans="1:11" s="12" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>23</v>
@@ -3272,10 +3420,10 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>130</v>
@@ -3286,13 +3434,13 @@
     </row>
     <row r="9" spans="1:11" s="11" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>23</v>
@@ -3304,10 +3452,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>131</v>
@@ -3318,13 +3466,13 @@
     </row>
     <row r="10" spans="1:11" s="11" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>23</v>
@@ -3336,10 +3484,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>133</v>
@@ -3350,13 +3498,13 @@
     </row>
     <row r="11" spans="1:11" s="11" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>23</v>
@@ -3368,10 +3516,10 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>134</v>
@@ -3382,13 +3530,13 @@
     </row>
     <row r="12" spans="1:11" s="11" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="22" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>23</v>
@@ -3397,30 +3545,30 @@
         <v>122</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J12" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="11" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>23</v>
@@ -3432,27 +3580,27 @@
         <v>3</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J13" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="11" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>23</v>
@@ -3464,21 +3612,21 @@
         <v>4</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>23</v>
@@ -3490,21 +3638,21 @@
         <v>4</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>23</v>
@@ -3516,21 +3664,21 @@
         <v>4</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>23</v>
@@ -3542,21 +3690,21 @@
         <v>5</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>23</v>
@@ -3568,21 +3716,21 @@
         <v>5</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>23</v>
@@ -3594,21 +3742,21 @@
         <v>5</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>23</v>
@@ -3620,21 +3768,21 @@
         <v>6</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>23</v>
@@ -3646,21 +3794,21 @@
         <v>6</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>23</v>
@@ -3672,21 +3820,21 @@
         <v>6</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="22" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>23</v>
@@ -3695,24 +3843,24 @@
         <v>56</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="22" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>96</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>23</v>
@@ -3721,24 +3869,24 @@
         <v>56</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="22" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>23</v>
@@ -3747,24 +3895,24 @@
         <v>56</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="22" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>23</v>
@@ -3773,24 +3921,24 @@
         <v>56</v>
       </c>
       <c r="F26" s="23" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="22" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>23</v>
@@ -3799,24 +3947,24 @@
         <v>56</v>
       </c>
       <c r="F27" s="23" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="22" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>23</v>
@@ -3825,24 +3973,24 @@
         <v>121</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="22" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>23</v>
@@ -3851,24 +3999,24 @@
         <v>123</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="22" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>67</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>23</v>
@@ -3877,24 +4025,24 @@
         <v>121</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="22" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>100</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>23</v>
@@ -3903,24 +4051,24 @@
         <v>121</v>
       </c>
       <c r="F31" s="23" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="36" t="s">
-        <v>248</v>
+      <c r="A32" s="22" t="s">
+        <v>247</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>23</v>
@@ -3929,24 +4077,24 @@
         <v>39</v>
       </c>
       <c r="F32" s="23" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="36" t="s">
-        <v>248</v>
+      <c r="A33" s="22" t="s">
+        <v>247</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>102</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>23</v>
@@ -3955,18 +4103,192 @@
         <v>39</v>
       </c>
       <c r="F33" s="23" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="35" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="36" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="F34" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="F35" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="F36" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F37" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F38" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="36" t="s">
+        <v>263</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C39" s="36" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="36" t="s">
+        <v>263</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C40" s="36" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="36" t="s">
+        <v>263</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C41" s="36" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="36" t="s">
+        <v>263</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C42" s="36" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="44" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="45" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="1048575" spans="7:8" x14ac:dyDescent="0.45">
       <c r="G1048575" s="1"/>
       <c r="H1048575" s="20"/>
@@ -3978,91 +4300,135 @@
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="G1:H1"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B11">
-    <cfRule type="duplicateValues" dxfId="46" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14">
-    <cfRule type="duplicateValues" dxfId="44" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15">
-    <cfRule type="duplicateValues" dxfId="42" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="40" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17">
+    <cfRule type="duplicateValues" dxfId="53" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B18">
+    <cfRule type="duplicateValues" dxfId="51" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19">
+    <cfRule type="duplicateValues" dxfId="49" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B20">
+    <cfRule type="duplicateValues" dxfId="47" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21">
+    <cfRule type="duplicateValues" dxfId="45" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="43" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23">
+    <cfRule type="duplicateValues" dxfId="41" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24">
     <cfRule type="duplicateValues" dxfId="39" priority="45"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="38" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B18">
-    <cfRule type="duplicateValues" dxfId="36" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19">
-    <cfRule type="duplicateValues" dxfId="34" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B20">
-    <cfRule type="duplicateValues" dxfId="32" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="35"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="30" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="33"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="28" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B23">
-    <cfRule type="duplicateValues" dxfId="26" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B24">
-    <cfRule type="duplicateValues" dxfId="24" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="duplicateValues" dxfId="22" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="18" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="16" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="14" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32:B33">
+    <cfRule type="duplicateValues" dxfId="25" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B37">
+    <cfRule type="duplicateValues" dxfId="23" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38">
+    <cfRule type="duplicateValues" dxfId="20" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3:K8 K10">
+    <cfRule type="duplicateValues" dxfId="18" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K11">
+    <cfRule type="duplicateValues" dxfId="17" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K12">
+    <cfRule type="duplicateValues" dxfId="16" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B39">
+    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B39">
+    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B39">
+    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B40">
+    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B40">
+    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B40">
+    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B41">
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B41">
     <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B32:B33">
-    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K3:K8 K10">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K12">
+  <conditionalFormatting sqref="B41">
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4097,26 +4463,26 @@
         <v>20</v>
       </c>
       <c r="F1" s="24"/>
-      <c r="H1" s="29" t="s">
+      <c r="H1" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="30"/>
+      <c r="I1" s="35"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>207</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>208</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F2" s="18" t="s">
         <v>15</v>
@@ -4130,20 +4496,20 @@
     </row>
     <row r="3" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
         <v>132</v>
       </c>
       <c r="E3" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>193</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>194</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>125</v>
@@ -4154,22 +4520,22 @@
     </row>
     <row r="4" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E4" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="F4" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>126</v>
@@ -4180,10 +4546,10 @@
     </row>
     <row r="5" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="C5" s="1">
         <v>3</v>
@@ -4192,10 +4558,10 @@
         <v>136</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>127</v>
@@ -4206,22 +4572,22 @@
     </row>
     <row r="6" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C6" s="1">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>128</v>
@@ -4232,20 +4598,20 @@
     </row>
     <row r="7" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>129</v>
@@ -4256,20 +4622,20 @@
     </row>
     <row r="8" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>130</v>
@@ -4280,20 +4646,20 @@
     </row>
     <row r="9" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="22" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>131</v>
@@ -4304,22 +4670,22 @@
     </row>
     <row r="10" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C10" s="1">
         <v>1</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>133</v>
@@ -4330,22 +4696,22 @@
     </row>
     <row r="11" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="22" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C11" s="1">
         <v>2</v>
       </c>
       <c r="D11" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F11" s="9" t="s">
         <v>205</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>206</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>134</v>
@@ -4356,175 +4722,210 @@
     </row>
     <row r="12" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C12" s="1">
         <v>3</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H12" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="22" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C14" s="19"/>
       <c r="D14" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J14" s="13"/>
     </row>
     <row r="15" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="22" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C15" s="19"/>
       <c r="D15" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="F15" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="22" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C16" s="19"/>
       <c r="D16" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="F16" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="22" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C17" s="19"/>
       <c r="D17" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>239</v>
-      </c>
       <c r="F17" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="22" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C18" s="19"/>
       <c r="D18" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="F18" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="36" t="s">
-        <v>248</v>
-      </c>
-      <c r="B19" s="37" t="s">
-        <v>251</v>
+      <c r="A19" s="22" t="s">
+        <v>247</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>250</v>
       </c>
       <c r="C19" s="19"/>
       <c r="D19" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="F19" s="9" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="21" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.45"/>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C20" s="1">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="36" t="s">
+        <v>263</v>
+      </c>
+      <c r="B21" s="36" t="s">
+        <v>265</v>
+      </c>
+      <c r="C21" s="19"/>
+      <c r="D21" s="36" t="s">
+        <v>262</v>
+      </c>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+    </row>
     <row r="22" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="H1:I1"/>
   </mergeCells>
+  <conditionalFormatting sqref="A3:A20 A22:A41">
+    <cfRule type="duplicateValues" dxfId="15" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I3:I8 I10">
-    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I11">
-    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
